--- a/Datas/Prop.xlsx
+++ b/Datas/Prop.xlsx
@@ -115,7 +115,7 @@
     <t>在范围内持续造成伤害</t>
   </si>
   <si>
-    <t>Arts/UI/Gameplay/Props/Prop_Bombardment</t>
+    <t>Arts/Props/UI/Prop_Bombardment</t>
   </si>
   <si>
     <t>示例</t>
@@ -130,7 +130,7 @@
     <t>自动锁定并跟随目标</t>
   </si>
   <si>
-    <t>Arts/UI/Gameplay/Props/Prop_AimAssist</t>
+    <t>Arts/Props/UI/Prop_AimAssist</t>
   </si>
   <si>
     <t>Trap</t>
@@ -142,7 +142,7 @@
     <t>生成陷阱吸引并击杀动物</t>
   </si>
   <si>
-    <t>Arts/UI/Gameplay/Props/Prop_Trap</t>
+    <t>Arts/Props/UI/Prop_Trap</t>
   </si>
 </sst>
 </file>

--- a/Datas/Prop.xlsx
+++ b/Datas/Prop.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -115,7 +115,7 @@
     <t>在范围内持续造成伤害</t>
   </si>
   <si>
-    <t>Arts/Props/UI/Prop_Bombardment</t>
+    <t>Assets/Arts/UI/Sprites/Gameplay/Prop/img_DJ_pao_0003</t>
   </si>
   <si>
     <t>示例</t>
@@ -130,7 +130,7 @@
     <t>自动锁定并跟随目标</t>
   </si>
   <si>
-    <t>Arts/Props/UI/Prop_AimAssist</t>
+    <t>Assets/Arts/UI/Sprites/Gameplay/Prop/img_DJ_miaozhunjin_0002</t>
   </si>
   <si>
     <t>Trap</t>
@@ -142,7 +142,7 @@
     <t>生成陷阱吸引并击杀动物</t>
   </si>
   <si>
-    <t>Arts/Props/UI/Prop_Trap</t>
+    <t>Assets/Arts/UI/Sprites/Gameplay/Prop/img_DJ_bushoujia_0001</t>
   </si>
 </sst>
 </file>
@@ -1104,7 +1104,7 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="6"/>
   <cols>
     <col min="1" max="6" width="28.625" customWidth="1"/>
-    <col min="7" max="7" width="56.625" customWidth="1"/>
+    <col min="7" max="7" width="78.625" customWidth="1"/>
     <col min="8" max="9" width="28.625" customWidth="1"/>
   </cols>
   <sheetData>

--- a/Datas/Prop.xlsx
+++ b/Datas/Prop.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="33">
   <si>
     <t>##var</t>
   </si>
@@ -49,9 +49,6 @@
     <t>Duration</t>
   </si>
   <si>
-    <t>IconResourcePath</t>
-  </si>
-  <si>
     <t>ParamTableID</t>
   </si>
   <si>
@@ -97,9 +94,6 @@
     <t>持续时间（秒）</t>
   </si>
   <si>
-    <t>图标资源路径</t>
-  </si>
-  <si>
     <t>参数子表ID</t>
   </si>
   <si>
@@ -115,9 +109,6 @@
     <t>在范围内持续造成伤害</t>
   </si>
   <si>
-    <t>Assets/Arts/UI/Sprites/Gameplay/Prop/img_DJ_pao_0003</t>
-  </si>
-  <si>
     <t>示例</t>
   </si>
   <si>
@@ -130,9 +121,6 @@
     <t>自动锁定并跟随目标</t>
   </si>
   <si>
-    <t>Assets/Arts/UI/Sprites/Gameplay/Prop/img_DJ_miaozhunjin_0002</t>
-  </si>
-  <si>
     <t>Trap</t>
   </si>
   <si>
@@ -140,9 +128,6 @@
   </si>
   <si>
     <t>生成陷阱吸引并击杀动物</t>
-  </si>
-  <si>
-    <t>Assets/Arts/UI/Sprites/Gameplay/Prop/img_DJ_bushoujia_0001</t>
   </si>
 </sst>
 </file>
@@ -1100,15 +1085,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="6"/>
+  <dimension ref="A1:H7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="6" outlineLevelCol="7"/>
   <cols>
-    <col min="1" max="6" width="28.625" customWidth="1"/>
-    <col min="7" max="7" width="78.625" customWidth="1"/>
-    <col min="8" max="9" width="28.625" customWidth="1"/>
+    <col min="1" max="2" width="28.625" customWidth="1"/>
+    <col min="3" max="3" width="48.625" customWidth="1"/>
+    <col min="4" max="8" width="28.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1" spans="1:9">
+    <row r="1" ht="28" customHeight="1" spans="1:8">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1133,176 +1118,155 @@
       <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+    </row>
+    <row r="2" ht="28" customHeight="1" spans="1:8">
+      <c r="A2" s="1" t="s">
         <v>8</v>
       </c>
+      <c r="B2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
-    <row r="2" ht="28" customHeight="1" spans="1:9">
-      <c r="A2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F2" s="1" t="s">
+    <row r="3" ht="28" customHeight="1" spans="1:8">
+      <c r="A3" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G2" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>12</v>
+      <c r="B3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>14</v>
       </c>
     </row>
-    <row r="3" ht="28" customHeight="1" spans="1:9">
-      <c r="A3" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B3" s="1" t="s">
+    <row r="4" ht="28" customHeight="1" spans="1:8">
+      <c r="A4" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>15</v>
+      <c r="B4" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>22</v>
       </c>
     </row>
-    <row r="4" ht="28" customHeight="1" spans="1:9">
-      <c r="A4" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="5" ht="28" customHeight="1" spans="1:9">
+    <row r="5" ht="28" customHeight="1" spans="1:8">
       <c r="A5" s="2"/>
       <c r="B5" s="2">
         <v>1</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>25</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>27</v>
       </c>
       <c r="F5" s="2">
         <v>6</v>
       </c>
-      <c r="G5" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="H5" s="2">
+      <c r="G5" s="2">
         <v>1</v>
       </c>
-      <c r="I5" s="2" t="s">
-        <v>29</v>
+      <c r="H5" s="2" t="s">
+        <v>26</v>
       </c>
     </row>
-    <row r="6" ht="28" customHeight="1" spans="1:9">
+    <row r="6" ht="28" customHeight="1" spans="1:8">
       <c r="A6" s="2"/>
       <c r="B6" s="2">
         <v>2</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F6" s="2">
         <v>30</v>
       </c>
-      <c r="G6" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="H6" s="2">
+      <c r="G6" s="2">
         <v>1</v>
       </c>
-      <c r="I6" s="2" t="s">
-        <v>29</v>
+      <c r="H6" s="2" t="s">
+        <v>26</v>
       </c>
     </row>
-    <row r="7" ht="28" customHeight="1" spans="1:9">
+    <row r="7" ht="28" customHeight="1" spans="1:8">
       <c r="A7" s="2"/>
       <c r="B7" s="2">
         <v>3</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="F7" s="2">
         <v>0</v>
       </c>
-      <c r="G7" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="H7" s="2">
+      <c r="G7" s="2">
         <v>1</v>
       </c>
-      <c r="I7" s="2" t="s">
-        <v>29</v>
+      <c r="H7" s="2" t="s">
+        <v>26</v>
       </c>
     </row>
   </sheetData>

--- a/Datas/Prop.xlsx
+++ b/Datas/Prop.xlsx
@@ -1260,7 +1260,7 @@
         <v>32</v>
       </c>
       <c r="F7" s="2">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="G7" s="2">
         <v>1</v>

--- a/Datas/Prop.xlsx
+++ b/Datas/Prop.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="30">
   <si>
     <t>##var</t>
   </si>
@@ -52,9 +52,6 @@
     <t>ParamTableID</t>
   </si>
   <si>
-    <t>Comment</t>
-  </si>
-  <si>
     <t>##type</t>
   </si>
   <si>
@@ -97,9 +94,6 @@
     <t>参数子表ID</t>
   </si>
   <si>
-    <t>备注</t>
-  </si>
-  <si>
     <t>Bombardment</t>
   </si>
   <si>
@@ -107,9 +101,6 @@
   </si>
   <si>
     <t>在范围内持续造成伤害</t>
-  </si>
-  <si>
-    <t>示例</t>
   </si>
   <si>
     <t>AimAssist</t>
@@ -1085,15 +1076,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="6" outlineLevelCol="7"/>
+  <dimension ref="A1:G7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="6" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="2" width="28.625" customWidth="1"/>
     <col min="3" max="3" width="48.625" customWidth="1"/>
-    <col min="4" max="8" width="28.625" customWidth="1"/>
+    <col min="4" max="7" width="28.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1" spans="1:8">
+    <row r="1" ht="28" customHeight="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1115,101 +1106,89 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+    </row>
+    <row r="2" ht="28" customHeight="1" spans="1:7">
+      <c r="A2" s="1" t="s">
         <v>7</v>
       </c>
+      <c r="B2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="2" ht="28" customHeight="1" spans="1:8">
-      <c r="A2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F2" s="1" t="s">
+    <row r="3" ht="28" customHeight="1" spans="1:7">
+      <c r="A3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="G2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>11</v>
+      <c r="B3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>13</v>
       </c>
     </row>
-    <row r="3" ht="28" customHeight="1" spans="1:8">
-      <c r="A3" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B3" s="1" t="s">
+    <row r="4" ht="28" customHeight="1" spans="1:7">
+      <c r="A4" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>14</v>
+      <c r="B4" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>20</v>
       </c>
     </row>
-    <row r="4" ht="28" customHeight="1" spans="1:8">
-      <c r="A4" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="5" ht="28" customHeight="1" spans="1:8">
+    <row r="5" ht="28" customHeight="1" spans="1:7">
       <c r="A5" s="2"/>
       <c r="B5" s="2">
         <v>1</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>23</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>25</v>
       </c>
       <c r="F5" s="2">
         <v>6</v>
@@ -1217,23 +1196,20 @@
       <c r="G5" s="2">
         <v>1</v>
       </c>
-      <c r="H5" s="2" t="s">
-        <v>26</v>
-      </c>
     </row>
-    <row r="6" ht="28" customHeight="1" spans="1:8">
+    <row r="6" ht="28" customHeight="1" spans="1:7">
       <c r="A6" s="2"/>
       <c r="B6" s="2">
         <v>2</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F6" s="2">
         <v>30</v>
@@ -1241,32 +1217,26 @@
       <c r="G6" s="2">
         <v>1</v>
       </c>
-      <c r="H6" s="2" t="s">
-        <v>26</v>
-      </c>
     </row>
-    <row r="7" ht="28" customHeight="1" spans="1:8">
+    <row r="7" ht="28" customHeight="1" spans="1:7">
       <c r="A7" s="2"/>
       <c r="B7" s="2">
         <v>3</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F7" s="2">
         <v>0.5</v>
       </c>
       <c r="G7" s="2">
         <v>1</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>26</v>
       </c>
     </row>
   </sheetData>
